--- a/lead_generation_forms/016_treadmill_product_information_request_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/016_treadmill_product_information_request_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_1':_'beginner'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_1': 'Beginner'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_2':_'intermediate'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_2': 'Intermediate'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_3':_'advanced'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_3': 'Advanced'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_1':_'home'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_1': 'Home'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_2':_'commercial'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_2': 'Commercial'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option_1':_'email'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option_1': 'Email'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option_2':_'phone'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option_2': 'Phone'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option_3':_'mail'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option_3': 'Mail'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option_1':_'online_ad'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option_1': 'Online Ad'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option_2':_'social_media'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option_2': 'Social Media'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option_3':_'referral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option_3': 'Referral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option_4':_'store_visit'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option_4': 'Store Visit'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option_5':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option_5': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option_1':_'sales'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option_1': 'Sales'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option_2':_'repair'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option_2': 'Repair'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option_3':_'maintenance'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option_3': 'Maintenance'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option_4':_'installation'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option_4': 'Installation'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option_5':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option_5': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option_1':_'google'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option_1': 'Google'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option_2':_'facebook'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option_2': 'Facebook'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option_3':_'instagram'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option_3': 'Instagram'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option_4':_'yelp'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option_4': 'Yelp'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option_5':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option_5': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option_1':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option_1': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option_2':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option_2': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
